--- a/data/gfallone.xlsx
+++ b/data/gfallone.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\OneDrive\Documentos\Proyectos\FIFI\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d3c7c81f20a53ce1/Documentos/Proyectos/FIFI/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9643B17C-6CFC-479A-B80F-2434B377C1C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{9643B17C-6CFC-479A-B80F-2434B377C1C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15458D0D-02AC-4C7E-B335-A29FEF2444BB}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{739F3CFD-7813-4989-A5C2-D54ADC38ABF3}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="17">
   <si>
     <t>Fecha</t>
   </si>
@@ -477,7 +477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F04C53F4-E46A-4F6C-8BD6-1FE17CDE865A}">
-  <dimension ref="A1:N64"/>
+  <dimension ref="A1:N67"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="16.44140625" bestFit="1" customWidth="1"/>
@@ -3370,33 +3370,174 @@
         <f t="shared" si="88"/>
         <v>64718.525000000001</v>
       </c>
+      <c r="G64" s="4">
+        <v>836.65</v>
+      </c>
       <c r="H64" s="5">
         <f t="shared" si="96"/>
-        <v>54247.369999999981</v>
+        <v>55084.019999999982</v>
       </c>
       <c r="I64" s="5">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>83.665000000000006</v>
       </c>
       <c r="J64" s="5">
         <f t="shared" si="98"/>
-        <v>3837.8449999999998</v>
+        <v>3921.5099999999998</v>
       </c>
       <c r="K64" s="5">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>752.98500000000001</v>
       </c>
       <c r="L64" s="5">
         <f t="shared" si="100"/>
-        <v>50409.525000000023</v>
+        <v>51162.510000000024</v>
       </c>
       <c r="M64" s="5">
         <f t="shared" si="101"/>
-        <v>0</v>
+        <v>25.099499999999999</v>
       </c>
       <c r="N64" s="6">
         <f t="shared" si="102"/>
-        <v>0</v>
+        <v>1.2927519593501241E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A65" s="3">
+        <v>46114</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D65" s="4">
+        <f t="shared" ref="D65:D67" si="103">+D64+K64+E64-F64</f>
+        <v>65471.51</v>
+      </c>
+      <c r="G65" s="4">
+        <v>435.65</v>
+      </c>
+      <c r="H65" s="5">
+        <f t="shared" ref="H65:H67" si="104">+H64+G65</f>
+        <v>55519.669999999984</v>
+      </c>
+      <c r="I65" s="5">
+        <f t="shared" ref="I65:I67" si="105">+G65*0.1</f>
+        <v>43.564999999999998</v>
+      </c>
+      <c r="J65" s="5">
+        <f t="shared" ref="J65:J67" si="106">+J64+I65</f>
+        <v>3965.0749999999998</v>
+      </c>
+      <c r="K65" s="5">
+        <f t="shared" ref="K65:K67" si="107">+G65-I65</f>
+        <v>392.08499999999998</v>
+      </c>
+      <c r="L65" s="5">
+        <f t="shared" ref="L65:L67" si="108">+L64+K65</f>
+        <v>51554.595000000023</v>
+      </c>
+      <c r="M65" s="5">
+        <f t="shared" ref="M65:M67" si="109">+K65/30</f>
+        <v>13.0695</v>
+      </c>
+      <c r="N65" s="6">
+        <f t="shared" ref="N65:N67" si="110">+G65/D65</f>
+        <v>6.6540392912886838E-3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A66" s="3">
+        <v>46144</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D66" s="4">
+        <f t="shared" si="103"/>
+        <v>65863.595000000001</v>
+      </c>
+      <c r="G66" s="4">
+        <v>1570.77</v>
+      </c>
+      <c r="H66" s="5">
+        <f t="shared" si="104"/>
+        <v>57090.439999999981</v>
+      </c>
+      <c r="I66" s="5">
+        <f t="shared" si="105"/>
+        <v>157.077</v>
+      </c>
+      <c r="J66" s="5">
+        <f t="shared" si="106"/>
+        <v>4122.152</v>
+      </c>
+      <c r="K66" s="5">
+        <f t="shared" si="107"/>
+        <v>1413.693</v>
+      </c>
+      <c r="L66" s="5">
+        <f t="shared" si="108"/>
+        <v>52968.288000000022</v>
+      </c>
+      <c r="M66" s="5">
+        <f t="shared" si="109"/>
+        <v>47.123100000000001</v>
+      </c>
+      <c r="N66" s="6">
+        <f t="shared" si="110"/>
+        <v>2.3848834853305533E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A67" s="3">
+        <v>46175</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D67" s="4">
+        <f t="shared" si="103"/>
+        <v>67277.288</v>
+      </c>
+      <c r="G67" s="4">
+        <v>1221.44</v>
+      </c>
+      <c r="H67" s="5">
+        <f t="shared" si="104"/>
+        <v>58311.879999999983</v>
+      </c>
+      <c r="I67" s="5">
+        <f t="shared" si="105"/>
+        <v>122.14400000000001</v>
+      </c>
+      <c r="J67" s="5">
+        <f t="shared" si="106"/>
+        <v>4244.2960000000003</v>
+      </c>
+      <c r="K67" s="5">
+        <f t="shared" si="107"/>
+        <v>1099.296</v>
+      </c>
+      <c r="L67" s="5">
+        <f t="shared" si="108"/>
+        <v>54067.584000000024</v>
+      </c>
+      <c r="M67" s="5">
+        <f t="shared" si="109"/>
+        <v>36.6432</v>
+      </c>
+      <c r="N67" s="6">
+        <f t="shared" si="110"/>
+        <v>1.8155309708679103E-2</v>
       </c>
     </row>
   </sheetData>
